--- a/sources/bryan_step10.xlsx
+++ b/sources/bryan_step10.xlsx
@@ -6836,11 +6836,6 @@
           <t>JG</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>TRUE</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>bcfea26d-eec1-4e77-a327-5ff22d064f6e</t>

--- a/sources/bryan_step10.xlsx
+++ b/sources/bryan_step10.xlsx
@@ -883,6 +883,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>74993c60-9c25-4ff3-b3fa-f1296b65505c</t>
+        </is>
+      </c>
       <c r="AB6" t="inlineStr">
         <is>
           <t>74993c60-9c25-4ff3-b3fa-f1296b65505c</t>
@@ -950,6 +955,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>09ebf217-6f8c-49a1-9120-b6d903c7cee0</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
           <t>09ebf217-6f8c-49a1-9120-b6d903c7cee0</t>
@@ -1020,6 +1030,11 @@
       <c r="Z8" t="inlineStr">
         <is>
           <t>TRUE</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>e28da776-8eb0-403d-bcb0-31b6cdece7b8</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -10108,6 +10123,11 @@
           <t>hmmmhhhhmh</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>1e24fe73-69af-4506-9a4b-0118515b9e02</t>
+        </is>
+      </c>
       <c r="AB108" t="inlineStr">
         <is>
           <t>1e24fe73-69af-4506-9a4b-0118515b9e02</t>
@@ -10160,6 +10180,11 @@
           <t>hmmmhhhm</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>ef6f4e30-fc93-476d-aa40-bed23e6e262d</t>
+        </is>
+      </c>
       <c r="AB109" t="inlineStr">
         <is>
           <t>ef6f4e30-fc93-476d-aa40-bed23e6e262d</t>
@@ -10210,6 +10235,11 @@
       <c r="U110" t="inlineStr">
         <is>
           <t>hmmmhhmh</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>f4a77540-d285-4628-a209-f8f0a4fbebf3</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
